--- a/src/lib/content/Living bibliography demo content-v0.5.xlsx
+++ b/src/lib/content/Living bibliography demo content-v0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mhal9222/Desktop/living-bibliography/src/lib/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7658C443-C8CA-9B40-95CD-BFA118BDB81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCE9E59-0EE7-8D49-B915-C16825610CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15060" yWindow="500" windowWidth="23860" windowHeight="28300" xr2:uid="{62C1BFAF-8520-5D4C-BFE9-88B66F49E369}"/>
+    <workbookView xWindow="15060" yWindow="500" windowWidth="23860" windowHeight="28300" activeTab="1" xr2:uid="{62C1BFAF-8520-5D4C-BFE9-88B66F49E369}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>https://www.nytimes.com/2022/01/31/style/jeuje-zhoosh-zhuzh.html</t>
   </si>
   <si>
-    <t>Date added to bibliography</t>
-  </si>
-  <si>
     <t>What would the dorks say this is?</t>
   </si>
   <si>
@@ -543,6 +540,9 @@
   </si>
   <si>
     <t>demonstration</t>
+  </si>
+  <si>
+    <t>Date updated</t>
   </si>
 </sst>
 </file>
@@ -967,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08788AED-5B1A-3845-92D9-4AC8EBF0A781}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1005,18 +1005,26 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
+        <v>149</v>
+      </c>
+      <c r="B7" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>151</v>
+      </c>
+      <c r="B9" s="1">
+        <v>45566</v>
       </c>
     </row>
   </sheetData>
@@ -1026,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6608C388-4639-4F4E-9326-DC48CED4E1B6}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="53.28515625" bestFit="1" customWidth="1"/>
@@ -1036,12 +1044,11 @@
     <col min="6" max="6" width="42.7109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="43.7109375" customWidth="1"/>
     <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.140625" customWidth="1"/>
-    <col min="10" max="10" width="42.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="42.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1049,10 +1056,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>10</v>
@@ -1066,17 +1073,14 @@
       <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="51">
+      <c r="I1" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="51">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1090,27 +1094,24 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="1">
-        <v>45524</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="153">
+      <c r="I2" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="153">
       <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C3">
         <v>41.786006737841198</v>
@@ -1122,88 +1123,79 @@
         <v>2024</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1">
-        <v>45534</v>
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="34">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="34">
       <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="E4">
         <v>2024</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="102">
+      <c r="A5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J4" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="K4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="102">
-      <c r="A5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="J5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="187">
+      <c r="A6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="187">
-      <c r="A6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="C6">
         <v>-35.317884915959098</v>
@@ -1215,27 +1207,24 @@
         <v>45350</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="1">
-        <v>45534</v>
+      <c r="I6" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="34">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="34">
       <c r="A7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1243,27 +1232,24 @@
         <v>2024</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K7" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="68">
+        <v>44</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="68">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>20</v>
@@ -1272,27 +1258,24 @@
         <v>2016</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="34">
+      <c r="A9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="K8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="34">
-      <c r="A9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="C9">
         <v>-33.885265132921198</v>
@@ -1304,140 +1287,125 @@
         <v>2023</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="1">
-        <v>45534</v>
+      <c r="I9" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="34">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="34">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>2024</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" t="s">
         <v>56</v>
       </c>
-      <c r="G10" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="34">
+      <c r="I10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="34">
       <c r="A11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="85">
+      <c r="I11" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="85">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1">
         <v>41542</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="1">
-        <v>45534</v>
+        <v>61</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="51">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="51">
       <c r="A13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E13" s="1">
         <v>45216</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="255">
+      <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="255">
-      <c r="A14" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>-33.888134571475199</v>
@@ -1446,91 +1414,82 @@
         <v>151.19048123415499</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="51">
+        <v>63</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="51">
       <c r="A15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="E15">
         <v>2024</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="1">
-        <v>45534</v>
+        <v>78</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="119">
+      <c r="A16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="119">
-      <c r="A16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="136">
+    <row r="17" spans="1:10" ht="136">
       <c r="A17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C17">
         <v>-35.283067649078603</v>
@@ -1542,30 +1501,27 @@
         <v>2024</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="17">
+        <v>93</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="17">
       <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="C18">
         <v>-33.882501233053603</v>
@@ -1577,50 +1533,44 @@
         <v>45444</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="1">
-        <v>45534</v>
+        <v>88</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="34">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="34">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="1">
         <v>45324</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="17">
+      <c r="I19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="17">
       <c r="A20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="C20">
         <v>-33.885265132921198</v>
@@ -1632,141 +1582,126 @@
         <v>2024</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="221">
+      <c r="I20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="221">
       <c r="A21" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21">
         <v>2024</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="1">
-        <v>45534</v>
+        <v>107</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="85">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="85">
       <c r="A22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22">
         <v>2008</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="17">
+      <c r="A23" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="17">
-      <c r="A23" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="B23" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23">
         <v>2024</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="1">
-        <v>45534</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="68">
+        <v>113</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="68">
       <c r="A24" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24">
         <v>2024</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" s="1">
-        <v>45534</v>
+        <v>115</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10">
       <c r="A26" s="3"/>
     </row>
   </sheetData>
@@ -1819,32 +1754,32 @@
     </row>
     <row r="2" spans="1:3" ht="255">
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="102">
       <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="409.6">
       <c r="A4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="409.6">
@@ -1852,32 +1787,32 @@
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="409.6">
       <c r="A6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="404">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="409.6">
@@ -1885,18 +1820,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17">
       <c r="A9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="289">
@@ -1904,29 +1839,29 @@
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.6">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="409.6">
       <c r="A12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
